--- a/notes/Payroll Project Test Log - Emily Eisenhauer.xlsx
+++ b/notes/Payroll Project Test Log - Emily Eisenhauer.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2927227a20fbab87/SDEV268/Final Project/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2927227a20fbab87/SDEV268/Final Project/notes/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="8_{3B83E207-D609-4D41-8A7F-978D147D369E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{998030CB-3CC7-4066-A8B3-A48C6460B9C9}"/>
+  <xr:revisionPtr revIDLastSave="83" documentId="8_{3B83E207-D609-4D41-8A7F-978D147D369E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AC370CCE-3A3A-41C9-9B12-2D59F4664172}"/>
   <bookViews>
-    <workbookView xWindow="4440" yWindow="1860" windowWidth="21600" windowHeight="11295" xr2:uid="{F7042606-B0EA-4422-8AD8-7C57A255E500}"/>
+    <workbookView xWindow="-23490" yWindow="1140" windowWidth="21600" windowHeight="13470" xr2:uid="{F7042606-B0EA-4422-8AD8-7C57A255E500}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
   <si>
     <t>Test ID</t>
   </si>
@@ -57,6 +57,105 @@
   </si>
   <si>
     <t>Notes</t>
+  </si>
+  <si>
+    <t>Employee can access time entry screen</t>
+  </si>
+  <si>
+    <t>Employee can access current time period only - no future dates and no dates for closed payroll</t>
+  </si>
+  <si>
+    <t>Employee can enter daily hours worked</t>
+  </si>
+  <si>
+    <t>Daily hours worked are saved</t>
+  </si>
+  <si>
+    <t>Time Clock</t>
+  </si>
+  <si>
+    <t>Tax Calculation</t>
+  </si>
+  <si>
+    <t>Taxes are calculated correctly for hourly employee with single medical and no dependents</t>
+  </si>
+  <si>
+    <t>Taxes are calculated correctly for salary employee with single medical and no dependents</t>
+  </si>
+  <si>
+    <t>Taxes are calculated correctly for salary employee with single medical and dependents</t>
+  </si>
+  <si>
+    <t>Taxes are calculated correctly for hourly employee with single medical and dependents</t>
+  </si>
+  <si>
+    <t>Taxes are calculated correctly for salary employee with family medical and dependents</t>
+  </si>
+  <si>
+    <t>Taxes are calculated correctly for hourly employee with family medical and dependents</t>
+  </si>
+  <si>
+    <t>Overtime Calculation</t>
+  </si>
+  <si>
+    <t>Overtime calculated correctly for hourly employee with over 40 hours</t>
+  </si>
+  <si>
+    <t>No overtime calculated for hourly employee with 40 or fewer hours</t>
+  </si>
+  <si>
+    <t>No overtime calculated for salary employee with 40 or fewer hours</t>
+  </si>
+  <si>
+    <t>No overtime calculated for salary employee with over 40 hours</t>
+  </si>
+  <si>
+    <t>Login Security</t>
+  </si>
+  <si>
+    <t>Employee username is assigned correctly: firstname.lastname@company.com</t>
+  </si>
+  <si>
+    <t>Employee password is assigned correctly: birthdate with only digits and no leading 0 in month/day</t>
+  </si>
+  <si>
+    <t>Successful entry of employee username and password = access to employee screens</t>
+  </si>
+  <si>
+    <t>Successful entry of admin username and password = access to admin screens</t>
+  </si>
+  <si>
+    <t>Employee failed entry of username = error message "login failed; try again" and no access</t>
+  </si>
+  <si>
+    <t>Employee failed entry of password = error message "login failed; try again" and no access</t>
+  </si>
+  <si>
+    <t>Admin failed entry of username = error message "login failed; try again" and no access</t>
+  </si>
+  <si>
+    <t>Admin failed entry of password = error message "login failed; try again" and no access</t>
+  </si>
+  <si>
+    <t>Employee demographics screen</t>
+  </si>
+  <si>
+    <t>Employee ID is assigned correctly: department + - + employee count</t>
+  </si>
+  <si>
+    <t>date of birth validates age &gt;= 18</t>
+  </si>
+  <si>
+    <t>department - only accepts drop down options</t>
+  </si>
+  <si>
+    <t>pay type only accepts drop down options</t>
+  </si>
+  <si>
+    <t>gender only accepts drop down options</t>
+  </si>
+  <si>
+    <t>employee email is assigned correctly: firstname + lastname + employee count + @businessplace.com</t>
   </si>
 </sst>
 </file>
@@ -92,8 +191,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -109,6 +211,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -428,8 +534,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF466EBE-4C31-43FA-8D2A-E49302EA4510}">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.140625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -454,7 +569,209 @@
         <v>6</v>
       </c>
     </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C6" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C12" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C13" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C15" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C16" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C17" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C18" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C20" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C21" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C22" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C23" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C24" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C25" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C26" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C27" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B28" s="1"/>
+      <c r="C28" s="1"/>
+      <c r="D28" s="1"/>
+      <c r="E28" s="1"/>
+      <c r="F28" s="1"/>
+      <c r="G28" s="1"/>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C29" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C30" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C31" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C32" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="33" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C33" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="34" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C34" t="s">
+        <v>39</v>
+      </c>
+    </row>
   </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="A14:G14"/>
+    <mergeCell ref="A19:G19"/>
+    <mergeCell ref="A28:G28"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>